--- a/cari acik/cari_acik_son.xlsx
+++ b/cari acik/cari_acik_son.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,26 +425,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tarih</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Cari Islemler Hesabi</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Finans Hesabi</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Net Hata ve Noksan</t>
         </is>
@@ -1277,13 +1289,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-9687</v>
+        <v>-9824</v>
       </c>
       <c r="C54" t="n">
         <v>-13642</v>
       </c>
       <c r="D54" t="n">
-        <v>-3956</v>
+        <v>-3819</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1305,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-5140</v>
+        <v>-5261</v>
       </c>
       <c r="C55" t="n">
         <v>-3515</v>
       </c>
       <c r="D55" t="n">
-        <v>1654</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1321,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8367</v>
+        <v>8240</v>
       </c>
       <c r="C56" t="n">
         <v>8323</v>
       </c>
       <c r="D56" t="n">
-        <v>39</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1337,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-6567</v>
+        <v>-6744</v>
       </c>
       <c r="C57" t="n">
         <v>-12060</v>
       </c>
       <c r="D57" t="n">
-        <v>-5478</v>
+        <v>-5301</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1353,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-14178</v>
+        <v>-14273</v>
       </c>
       <c r="C58" t="n">
         <v>-14306</v>
       </c>
       <c r="D58" t="n">
-        <v>-148</v>
+        <v>-53</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1369,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-11820</v>
+        <v>-11743</v>
       </c>
       <c r="C59" t="n">
-        <v>-11932</v>
+        <v>-11947</v>
       </c>
       <c r="D59" t="n">
-        <v>-87</v>
+        <v>-179</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1385,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>6886</v>
+        <v>7027</v>
       </c>
       <c r="C60" t="n">
-        <v>8807</v>
+        <v>8730</v>
       </c>
       <c r="D60" t="n">
-        <v>2084</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1401,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-11226</v>
+        <v>-11141</v>
       </c>
       <c r="C61" t="n">
-        <v>-18984</v>
+        <v>-18986</v>
       </c>
       <c r="D61" t="n">
-        <v>-7785</v>
+        <v>-7872</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1417,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-23633</v>
+        <v>-23708</v>
       </c>
       <c r="C62" t="n">
-        <v>-37818</v>
+        <v>-37882</v>
       </c>
       <c r="D62" t="n">
-        <v>-14111</v>
+        <v>-14100</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1433,29 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-10915</v>
+        <v>-11158</v>
       </c>
       <c r="C63" t="n">
-        <v>-11568</v>
+        <v>-12057</v>
       </c>
       <c r="D63" t="n">
-        <v>-624</v>
+        <v>-870</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-Q3</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>36</v>
+      </c>
+      <c r="C64" t="n">
+        <v>549</v>
+      </c>
+      <c r="D64" t="n">
+        <v>620</v>
       </c>
     </row>
   </sheetData>

--- a/cari acik/cari_acik_son.xlsx
+++ b/cari acik/cari_acik_son.xlsx
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>-9824</v>
+        <v>-9809</v>
       </c>
       <c r="C54" t="n">
         <v>-13642</v>
       </c>
       <c r="D54" t="n">
-        <v>-3819</v>
+        <v>-3834</v>
       </c>
     </row>
     <row r="55">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-5261</v>
+        <v>-5258</v>
       </c>
       <c r="C55" t="n">
         <v>-3515</v>
       </c>
       <c r="D55" t="n">
-        <v>1775</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="56">
@@ -1309,13 +1309,13 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>8240</v>
+        <v>8232</v>
       </c>
       <c r="C56" t="n">
         <v>8323</v>
       </c>
       <c r="D56" t="n">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57">
@@ -1325,13 +1325,13 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>-6744</v>
+        <v>-6752</v>
       </c>
       <c r="C57" t="n">
         <v>-12060</v>
       </c>
       <c r="D57" t="n">
-        <v>-5301</v>
+        <v>-5293</v>
       </c>
     </row>
     <row r="58">
@@ -1341,13 +1341,13 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>-14273</v>
+        <v>-14267</v>
       </c>
       <c r="C58" t="n">
-        <v>-14306</v>
+        <v>-14233</v>
       </c>
       <c r="D58" t="n">
-        <v>-53</v>
+        <v>14</v>
       </c>
     </row>
     <row r="59">
@@ -1357,13 +1357,13 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>-11743</v>
+        <v>-11765</v>
       </c>
       <c r="C59" t="n">
-        <v>-11947</v>
+        <v>-11878</v>
       </c>
       <c r="D59" t="n">
-        <v>-179</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="60">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>7027</v>
+        <v>6949</v>
       </c>
       <c r="C60" t="n">
-        <v>8730</v>
+        <v>8680</v>
       </c>
       <c r="D60" t="n">
-        <v>1866</v>
+        <v>1894</v>
       </c>
     </row>
     <row r="61">
@@ -1389,13 +1389,13 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>-11141</v>
+        <v>-11193</v>
       </c>
       <c r="C61" t="n">
-        <v>-18986</v>
+        <v>-18888</v>
       </c>
       <c r="D61" t="n">
-        <v>-7872</v>
+        <v>-7722</v>
       </c>
     </row>
     <row r="62">
@@ -1405,13 +1405,13 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>-23708</v>
+        <v>-24002</v>
       </c>
       <c r="C62" t="n">
-        <v>-37882</v>
+        <v>-37879</v>
       </c>
       <c r="D62" t="n">
-        <v>-14100</v>
+        <v>-13803</v>
       </c>
     </row>
     <row r="63">
@@ -1421,13 +1421,13 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>-11158</v>
+        <v>-11460</v>
       </c>
       <c r="C63" t="n">
-        <v>-12057</v>
+        <v>-11921</v>
       </c>
       <c r="D63" t="n">
-        <v>-870</v>
+        <v>-432</v>
       </c>
     </row>
     <row r="64">
@@ -1437,13 +1437,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>36</v>
+        <v>3964</v>
       </c>
       <c r="C64" t="n">
-        <v>549</v>
+        <v>8836</v>
       </c>
       <c r="D64" t="n">
-        <v>620</v>
+        <v>5033</v>
       </c>
     </row>
   </sheetData>
